--- a/4994_Cuenca_Urubamba/_raw_reportes_xlsx/IDConfig_64951_completo.xlsx
+++ b/4994_Cuenca_Urubamba/_raw_reportes_xlsx/IDConfig_64951_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rc49ef132a03a4b6b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rc8a70a2fec034b40"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,141 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     24.6600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.1827</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.8345</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     32.2025</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     33.5317</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.9123</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.9628</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.9343</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.7452</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>14/08/2026</x:t>
         </x:is>
       </x:c>
@@ -264,7 +399,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     25.9681</x:v>
+        <x:v>     26.3498</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -564,192 +699,192 @@
         </x:is>
       </x:c>
       <x:c s="3">
+        <x:v>     26.5361</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.3465</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.6031</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.7954</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.6989</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.2529</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.4535</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.7324</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.7685</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.6475</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.4966</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.4072</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
         <x:v>     26.9237</x:v>
       </x:c>
     </x:row>
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>24/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     26.3465</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>23/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     26.6031</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>22/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     26.7954</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>21/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     27.0881</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>20/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     27.2529</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>19/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     27.4535</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>18/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     26.7324</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>17/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     26.7685</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>16/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     27.6475</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>15/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     26.4966</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>14/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     26.4072</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>13/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     26.9237</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
           <x:t>12/07/2026</x:t>
         </x:is>
       </x:c>
@@ -804,7 +939,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     29.2326</x:v>
+        <x:v>     29.6475</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -819,7 +954,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     30.3481</x:v>
+        <x:v>     29.9264</x:v>
       </x:c>
     </x:row>
     <x:row>
